--- a/data/trans_camb/IP25-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Clase-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-87,32</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-85,13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,39</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>-0,16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-86,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 9,48</t>
+          <t>-5,5; 9,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 6,98</t>
+          <t>-10,01; 6,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-92,15; -81,41</t>
+          <t>-2,79; 13,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 12,86</t>
+          <t>-6,36; 9,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 8,87</t>
+          <t>-2,17; 8,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-90,39; -78,86</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 8,9</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-5,74; 6,12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-90,09; -82,27</t>
+          <t>-5,43; 5,48</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>-0,18%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 11,43</t>
+          <t>-6,08; 11,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 8,34</t>
+          <t>-11,13; 7,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,06; 16,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 16,21</t>
+          <t>-7,17; 11,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 10,83</t>
+          <t>-2,37; 10,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-2,33; 10,61</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-6,55; 7,45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,08; 6,65</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-88,62</t>
+          <t>7,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-82,45</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,02</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>4,78</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-85,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 7,67</t>
+          <t>-6,64; 8,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 7,85</t>
+          <t>-6,33; 8,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-93,28; -82,26</t>
+          <t>-0,13; 15,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 15,53</t>
+          <t>1,58; 17,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,84</t>
+          <t>-1,2; 9,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-88,12; -75,45</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 9,42</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-0,48; 9,69</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-89,61; -81,04</t>
+          <t>-0,43; 10,11</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>5,58%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 9,32</t>
+          <t>-7,23; 10,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 9,4</t>
+          <t>-6,81; 9,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,12; 21,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 20,23</t>
+          <t>1,84; 22,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 21,53</t>
+          <t>-1,3; 11,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-1,74; 11,53</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 11,91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,46; 12,33</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-90,03</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-91,52</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>0,09</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-90,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 8,5</t>
+          <t>-6,63; 8,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 10,05</t>
+          <t>-5,46; 10,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-94,32; -83,4</t>
+          <t>-8,49; 5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 5,13</t>
+          <t>-8,83; 5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 5,44</t>
+          <t>-5,97; 4,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-95,05; -85,93</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,37; 4,96</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-5,99; 4,65</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-94,07; -86,84</t>
+          <t>-4,78; 5,47</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-1,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,37%</t>
+          <t>-1,63%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-1,63%</t>
+          <t>-0,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-0,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>0,1%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 9,89</t>
+          <t>-7,03; 9,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 11,63</t>
+          <t>-5,83; 11,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,01; 5,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 5,73</t>
+          <t>-9,43; 6,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 6,17</t>
+          <t>-6,42; 5,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-5,83; 5,66</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-6,4; 5,21</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,15; 6,12</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-91,04</t>
+          <t>4,63</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-88,25</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>2,02</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-89,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,53</t>
+          <t>-9,57; 0,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 3,85</t>
+          <t>-4,83; 4,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-93,74; -87,38</t>
+          <t>0,15; 8,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 9,24</t>
+          <t>0,02; 8,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 9,1</t>
+          <t>-3,08; 3,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-91,43; -84,21</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 3,4</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 5,52</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-91,97; -87,18</t>
+          <t>-1,09; 5,48</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>2,25%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 0,68</t>
+          <t>-10,39; 0,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,33</t>
+          <t>-5,15; 4,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,17; 10,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 10,78</t>
+          <t>0,07; 10,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 10,52</t>
+          <t>-3,4; 4,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-3,37; 3,86</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-1,47; 6,28</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-1,17; 6,21</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-93,18</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-87,43</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>0,8</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-90,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 1,26</t>
+          <t>-10,14; 1,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 4,36</t>
+          <t>-6,94; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-96,34; -88,22</t>
+          <t>-3,56; 9,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 8,99</t>
+          <t>-3,76; 9,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,4</t>
+          <t>-4,84; 3,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-91,42; -81,28</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 3,81</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-3,41; 5,22</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-93,15; -86,94</t>
+          <t>-3,33; 5,49</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>-0,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-0,8%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 1,32</t>
+          <t>-10,65; 1,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,85</t>
+          <t>-7,23; 4,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,88; 11,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 10,82</t>
+          <t>-4,15; 10,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 11,26</t>
+          <t>-5,25; 3,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-5,6; 4,38</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-3,66; 5,97</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-3,62; 6,28</t>
         </is>
       </c>
     </row>
@@ -1714,37 +1383,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-92,05</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-90,5</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
           <t>1,27</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>-91,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 5,08</t>
+          <t>-10,52; 5,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 5,27</t>
+          <t>-10,92; 4,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-96,06; -85,43</t>
+          <t>-8,76; 7,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 7,3</t>
+          <t>-1,49; 11,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 12,7</t>
+          <t>-7,17; 3,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-95,27; -83,58</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 4,5</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 6,42</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-94,36; -87,26</t>
+          <t>-4,13; 6,33</t>
         </is>
       </c>
     </row>
@@ -1820,37 +1459,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-0,76%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-0,76%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>-1,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-1,48%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
           <t>1,39%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 5,66</t>
+          <t>-11,14; 6,25</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 6,02</t>
+          <t>-11,54; 4,84</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,37; 8,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 8,62</t>
+          <t>-1,5; 14,07</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 15,14</t>
+          <t>-7,75; 4,38</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-7,81; 4,96</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-4,39; 7,2</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,44; 7,13</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1539,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-90,47</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-87,64</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
           <t>1,56</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-89,0</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,93</t>
+          <t>-4,65; 0,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,11</t>
+          <t>-2,95; 2,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-92,27; -88,52</t>
+          <t>0,53; 6,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,15</t>
+          <t>1,18; 6,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,16</t>
+          <t>-1,06; 2,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-89,85; -85,58</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-1,04; 2,85</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 3,4</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-90,29; -87,54</t>
+          <t>-0,5; 3,24</t>
         </is>
       </c>
     </row>
@@ -2036,37 +1615,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
           <t>1,76%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 1,06</t>
+          <t>-5,13; 0,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,36</t>
+          <t>-3,22; 2,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,61; 7,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,16</t>
+          <t>1,32; 7,69</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,14</t>
+          <t>-1,18; 2,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-1,16; 3,24</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 3,86</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,55; 3,69</t>
         </is>
       </c>
     </row>
@@ -2133,11 +1682,11 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/IP25-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 9,89</t>
+          <t>-5,64; 9,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 6,06</t>
+          <t>-11,04; 6,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 13,07</t>
+          <t>-2,5; 12,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 9,6</t>
+          <t>-6,68; 9,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 8,75</t>
+          <t>-2,19; 8,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 5,48</t>
+          <t>-5,87; 5,17</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 11,8</t>
+          <t>-6,19; 11,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 7,23</t>
+          <t>-12,3; 7,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 16,28</t>
+          <t>-2,74; 15,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 11,88</t>
+          <t>-7,38; 11,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,53</t>
+          <t>-2,39; 9,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 6,65</t>
+          <t>-6,63; 6,14</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 8,71</t>
+          <t>-6,36; 7,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 8,12</t>
+          <t>-6,29; 7,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 15,99</t>
+          <t>-0,35; 16,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 17,26</t>
+          <t>1,37; 16,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 9,5</t>
+          <t>-1,36; 9,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 10,11</t>
+          <t>-0,4; 10,19</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 10,35</t>
+          <t>-6,92; 9,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 9,72</t>
+          <t>-6,91; 9,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 21,08</t>
+          <t>-0,41; 20,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 22,66</t>
+          <t>1,59; 21,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 11,57</t>
+          <t>-1,41; 11,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 12,33</t>
+          <t>-0,44; 12,3</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 8,36</t>
+          <t>-7,0; 8,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 10,13</t>
+          <t>-6,28; 9,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 5,22</t>
+          <t>-10,17; 5,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 5,45</t>
+          <t>-9,03; 5,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 4,48</t>
+          <t>-5,9; 4,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,47</t>
+          <t>-5,54; 5,24</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 9,83</t>
+          <t>-7,44; 10,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 11,7</t>
+          <t>-6,61; 10,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 5,94</t>
+          <t>-11,0; 5,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 6,21</t>
+          <t>-9,63; 5,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,07</t>
+          <t>-6,37; 5,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 6,12</t>
+          <t>-5,94; 5,9</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 0,33</t>
+          <t>-9,56; 0,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 4,03</t>
+          <t>-4,65; 4,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 8,96</t>
+          <t>0,09; 9,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 8,99</t>
+          <t>0,17; 8,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,63</t>
+          <t>-3,11; 3,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,48</t>
+          <t>-1,1; 5,38</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 0,32</t>
+          <t>-10,4; 0,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 4,54</t>
+          <t>-4,96; 4,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 10,49</t>
+          <t>0,08; 11,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 10,57</t>
+          <t>0,18; 10,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,12</t>
+          <t>-3,44; 4,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,21</t>
+          <t>-1,21; 6,15</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 1,65</t>
+          <t>-10,67; 0,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 4,08</t>
+          <t>-7,54; 3,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 9,16</t>
+          <t>-3,15; 9,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 9,07</t>
+          <t>-3,32; 9,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 3,51</t>
+          <t>-4,95; 3,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,49</t>
+          <t>-3,45; 5,12</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 1,89</t>
+          <t>-11,23; 0,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,55</t>
+          <t>-7,95; 3,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 11,11</t>
+          <t>-3,35; 11,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 10,99</t>
+          <t>-3,66; 11,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 3,98</t>
+          <t>-5,36; 4,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 6,28</t>
+          <t>-3,72; 5,86</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 5,58</t>
+          <t>-9,94; 5,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 4,33</t>
+          <t>-10,89; 5,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 7,34</t>
+          <t>-8,85; 6,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 11,98</t>
+          <t>-1,27; 12,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 3,99</t>
+          <t>-7,18; 4,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 6,33</t>
+          <t>-4,39; 6,26</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 6,25</t>
+          <t>-10,56; 6,36</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 4,84</t>
+          <t>-11,9; 5,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 8,54</t>
+          <t>-9,39; 7,73</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 14,07</t>
+          <t>-1,21; 15,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 4,38</t>
+          <t>-7,76; 4,55</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 7,13</t>
+          <t>-4,63; 6,97</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,51</t>
+          <t>-4,51; 0,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,1</t>
+          <t>-3,55; 1,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,11</t>
+          <t>0,68; 6,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,67</t>
+          <t>0,83; 6,24</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,54</t>
+          <t>-1,22; 2,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,24</t>
+          <t>-0,22; 3,53</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 0,56</t>
+          <t>-4,94; 0,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,38</t>
+          <t>-3,86; 2,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,18</t>
+          <t>0,74; 6,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,69</t>
+          <t>0,9; 7,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,88</t>
+          <t>-1,36; 2,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,69</t>
+          <t>-0,24; 4,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP25-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-1,9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 9,35</t>
+          <t>-2,73; 12,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 6,18</t>
+          <t>-6,75; 8,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 12,64</t>
+          <t>-5,43; 9,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 9,06</t>
+          <t>-10,44; 6,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 8,12</t>
+          <t>-2,07; 8,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,17</t>
+          <t>-5,74; 6,12</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-2,18%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 11,24</t>
+          <t>-3,01; 16,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 7,42</t>
+          <t>-7,48; 10,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 15,67</t>
+          <t>-5,8; 11,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 11,37</t>
+          <t>-11,69; 8,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 9,89</t>
+          <t>-2,33; 10,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 6,14</t>
+          <t>-6,55; 7,45</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,35</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,87</t>
+          <t>-1,14; 15,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 7,83</t>
+          <t>1,8; 16,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 16,02</t>
+          <t>-6,61; 7,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 16,33</t>
+          <t>-6,32; 7,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 9,77</t>
+          <t>-1,56; 9,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 10,19</t>
+          <t>-0,48; 9,69</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 9,4</t>
+          <t>-1,24; 20,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 9,26</t>
+          <t>2,0; 21,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 20,65</t>
+          <t>-7,15; 9,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 21,56</t>
+          <t>-6,8; 9,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 11,82</t>
+          <t>-1,74; 11,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 12,3</t>
+          <t>-0,54; 11,91</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,55</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 8,65</t>
+          <t>-8,26; 5,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 9,06</t>
+          <t>-9,15; 5,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 5,28</t>
+          <t>-6,94; 8,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 5,19</t>
+          <t>-5,8; 10,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 4,47</t>
+          <t>-5,37; 4,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 5,24</t>
+          <t>-5,99; 4,65</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-1,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-1,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,37%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,63%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 10,26</t>
+          <t>-8,95; 5,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 10,71</t>
+          <t>-9,77; 6,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 5,93</t>
+          <t>-7,56; 9,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 5,87</t>
+          <t>-6,16; 11,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 5,04</t>
+          <t>-5,83; 5,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 5,9</t>
+          <t>-6,4; 5,21</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,51</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-4,21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,42</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,63</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,51</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 0,64</t>
+          <t>-0,16; 9,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 4,3</t>
+          <t>0,04; 9,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 9,56</t>
+          <t>-9,48; 0,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 8,96</t>
+          <t>-4,91; 3,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 3,72</t>
+          <t>-3,09; 3,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,38</t>
+          <t>-1,33; 5,52</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-4,63%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-0,46%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 0,72</t>
+          <t>-0,17; 10,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 4,86</t>
+          <t>0,03; 10,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 11,26</t>
+          <t>-10,16; 0,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 10,47</t>
+          <t>-5,32; 4,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,22</t>
+          <t>-3,37; 3,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,15</t>
+          <t>-1,47; 6,28</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,97</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-4,92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-1,91</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,97</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 0,66</t>
+          <t>-3,62; 8,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 3,34</t>
+          <t>-3,29; 9,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 9,36</t>
+          <t>-10,45; 1,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 9,44</t>
+          <t>-6,81; 4,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,83</t>
+          <t>-5,15; 3,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 5,12</t>
+          <t>-3,41; 5,22</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-5,28%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-2,05%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 0,72</t>
+          <t>-3,85; 10,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 3,69</t>
+          <t>-3,62; 11,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 11,42</t>
+          <t>-11,01; 1,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 11,18</t>
+          <t>-7,1; 4,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,37</t>
+          <t>-5,6; 4,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,86</t>
+          <t>-3,66; 5,97</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5,32</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-1,93</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-3,11</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5,32</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 5,68</t>
+          <t>-8,99; 7,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 5,07</t>
+          <t>-1,65; 12,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 6,71</t>
+          <t>-11,06; 5,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 12,65</t>
+          <t>-10,89; 5,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 4,07</t>
+          <t>-7,17; 4,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,26</t>
+          <t>-4,11; 6,42</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-0,76%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-2,09%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-3,38%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-0,76%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 6,36</t>
+          <t>-9,71; 8,62</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 5,79</t>
+          <t>-1,7; 15,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 7,73</t>
+          <t>-11,62; 5,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 15,02</t>
+          <t>-11,51; 6,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 4,55</t>
+          <t>-7,81; 4,96</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 6,97</t>
+          <t>-4,39; 7,2</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3,34</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-1,91</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,58</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3,57</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,78</t>
+          <t>0,73; 6,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,82</t>
+          <t>0,86; 6,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,02</t>
+          <t>-4,53; 0,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 6,24</t>
+          <t>-3,17; 2,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,58</t>
+          <t>-1,04; 2,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,53</t>
+          <t>-0,52; 3,4</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-2,12%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-0,64%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 0,88</t>
+          <t>0,84; 7,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,04</t>
+          <t>1,03; 7,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,9</t>
+          <t>-4,96; 1,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,22</t>
+          <t>-3,45; 2,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,92</t>
+          <t>-1,16; 3,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,0</t>
+          <t>-0,61; 3,86</t>
         </is>
       </c>
     </row>
